--- a/outputs/tables/tabla_estabilidad_semillas_advi.xlsx
+++ b/outputs/tables/tabla_estabilidad_semillas_advi.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
   <si>
     <t>Semilla</t>
   </si>
@@ -22,10 +22,10 @@
     <t>ELBO_Final</t>
   </si>
   <si>
-    <t>ELBO_Meseta_Media</t>
-  </si>
-  <si>
-    <t>Iteraciones</t>
+    <t>Variacion_ELBO_Ultimas_5k_Pct</t>
+  </si>
+  <si>
+    <t>Criterio_Convergencia</t>
   </si>
   <si>
     <t>Convergio</t>
@@ -49,22 +49,16 @@
     <t>beta_area_sd</t>
   </si>
   <si>
-    <t>sigma_s_media</t>
-  </si>
-  <si>
-    <t>sigma_s_sd</t>
-  </si>
-  <si>
-    <t>rho_media</t>
-  </si>
-  <si>
-    <t>rho_sd</t>
-  </si>
-  <si>
-    <t>rho_hdi_inf</t>
-  </si>
-  <si>
-    <t>rho_hdi_sup</t>
+    <t>sigma_phi_media</t>
+  </si>
+  <si>
+    <t>sigma_phi_sd</t>
+  </si>
+  <si>
+    <t>sigma_theta_media</t>
+  </si>
+  <si>
+    <t>sigma_theta_sd</t>
   </si>
   <si>
     <t>alpha_disp_media</t>
@@ -79,10 +73,16 @@
     <t>Desv. Est. (Entre Semillas)</t>
   </si>
   <si>
-    <t>Sí (100%)</t>
+    <t>Var 5k &lt; 0.1%</t>
   </si>
   <si>
     <t>-</t>
+  </si>
+  <si>
+    <t>Sí</t>
+  </si>
+  <si>
+    <t>Sí (3/3)</t>
   </si>
 </sst>
 </file>
@@ -440,10 +440,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S6"/>
+  <dimension ref="A1:Q6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -495,306 +495,270 @@
       <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>18</v>
-      </c>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:17">
       <c r="A2">
         <v>42</v>
       </c>
       <c r="B2">
-        <v>-3359.57</v>
+        <v>-1480.21</v>
       </c>
       <c r="C2">
-        <v>-1802.64</v>
-      </c>
-      <c r="D2">
-        <v>40000</v>
-      </c>
-      <c r="E2" t="b">
-        <v>0</v>
+        <v>0.0076</v>
+      </c>
+      <c r="D2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
       </c>
       <c r="F2">
-        <v>1.623524116197549</v>
+        <v>1.332005694650479</v>
       </c>
       <c r="G2">
-        <v>0.04491802682084656</v>
+        <v>0.02516312780517108</v>
       </c>
       <c r="H2">
-        <v>0.3174807836015135</v>
+        <v>0.3125963688782021</v>
       </c>
       <c r="I2">
-        <v>0.06132663748723281</v>
+        <v>0.03574931768889927</v>
       </c>
       <c r="J2">
-        <v>0.1139655428802458</v>
+        <v>0.3214628363099949</v>
       </c>
       <c r="K2">
-        <v>0.03163176786816241</v>
+        <v>0.02141195909625017</v>
       </c>
       <c r="L2">
-        <v>0.9326691078819246</v>
+        <v>2.558342875251677</v>
       </c>
       <c r="M2">
-        <v>0.04699295345166132</v>
+        <v>0.04939655817856773</v>
       </c>
       <c r="N2">
-        <v>0.02743806563775158</v>
+        <v>0.01922899493146631</v>
       </c>
       <c r="O2">
-        <v>0.04290666347412147</v>
+        <v>0.01548166862814764</v>
       </c>
       <c r="P2">
-        <v>0.0009044670208433613</v>
+        <v>7.098867776710443</v>
       </c>
       <c r="Q2">
-        <v>0.1484819000085819</v>
-      </c>
-      <c r="R2">
-        <v>1.895346243636717</v>
-      </c>
-      <c r="S2">
-        <v>0.1902601476808199</v>
+        <v>0.8997399849432262</v>
       </c>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" spans="1:17">
       <c r="A3">
         <v>123</v>
       </c>
       <c r="B3">
-        <v>-2487.22</v>
+        <v>-1410.77</v>
       </c>
       <c r="C3">
-        <v>-1770.63</v>
-      </c>
-      <c r="D3">
-        <v>40000</v>
-      </c>
-      <c r="E3" t="b">
-        <v>0</v>
+        <v>0.0638</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
       </c>
       <c r="F3">
-        <v>1.623778128408778</v>
+        <v>1.351918969314986</v>
       </c>
       <c r="G3">
-        <v>0.04584008542277374</v>
+        <v>0.02518978102619612</v>
       </c>
       <c r="H3">
-        <v>0.3157588275025591</v>
+        <v>0.319605347837042</v>
       </c>
       <c r="I3">
-        <v>0.06362749840830575</v>
+        <v>0.03630999987746104</v>
       </c>
       <c r="J3">
-        <v>0.1174209625611862</v>
+        <v>0.3161343921845154</v>
       </c>
       <c r="K3">
-        <v>0.03042671778153327</v>
+        <v>0.02059773163886027</v>
       </c>
       <c r="L3">
-        <v>0.9409101874383361</v>
+        <v>2.605343004977112</v>
       </c>
       <c r="M3">
-        <v>0.046780919908641</v>
+        <v>0.05651159955244913</v>
       </c>
       <c r="N3">
-        <v>0.02709636327193479</v>
+        <v>0.02047420476246393</v>
       </c>
       <c r="O3">
-        <v>0.04744799163816882</v>
+        <v>0.0175495252095893</v>
       </c>
       <c r="P3">
-        <v>0.0009279205806517582</v>
+        <v>7.204266652214683</v>
       </c>
       <c r="Q3">
-        <v>0.145583162857086</v>
-      </c>
-      <c r="R3">
-        <v>1.885934853597718</v>
-      </c>
-      <c r="S3">
-        <v>0.1876216406785289</v>
+        <v>0.9431206763929584</v>
       </c>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" spans="1:17">
       <c r="A4">
         <v>999</v>
       </c>
       <c r="B4">
-        <v>-1643.06</v>
+        <v>-1427.04</v>
       </c>
       <c r="C4">
-        <v>-1816.74</v>
-      </c>
-      <c r="D4">
-        <v>40000</v>
-      </c>
-      <c r="E4" t="b">
-        <v>0</v>
+        <v>0.0578</v>
+      </c>
+      <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
       </c>
       <c r="F4">
-        <v>1.628772147178876</v>
+        <v>1.332831010468481</v>
       </c>
       <c r="G4">
-        <v>0.04522113317609407</v>
+        <v>0.02625027291831595</v>
       </c>
       <c r="H4">
-        <v>0.315314504040495</v>
+        <v>0.3112868222927571</v>
       </c>
       <c r="I4">
-        <v>0.05965156012589985</v>
+        <v>0.03383968101270034</v>
       </c>
       <c r="J4">
-        <v>0.1161786593041603</v>
+        <v>0.3255962606921124</v>
       </c>
       <c r="K4">
-        <v>0.03122912729683145</v>
+        <v>0.01962156322285576</v>
       </c>
       <c r="L4">
-        <v>0.9323345727414417</v>
+        <v>2.605821791190158</v>
       </c>
       <c r="M4">
-        <v>0.04684206540636381</v>
+        <v>0.05622828872385578</v>
       </c>
       <c r="N4">
-        <v>0.02661597530497388</v>
+        <v>0.01894117873855222</v>
       </c>
       <c r="O4">
-        <v>0.04251419240636662</v>
+        <v>0.01417912455200152</v>
       </c>
       <c r="P4">
-        <v>0.0008799909937939831</v>
+        <v>7.252540700545737</v>
       </c>
       <c r="Q4">
-        <v>0.1497816357182009</v>
-      </c>
-      <c r="R4">
-        <v>1.862355073398196</v>
-      </c>
-      <c r="S4">
-        <v>0.1884001193438192</v>
+        <v>0.9228097371502897</v>
       </c>
     </row>
-    <row r="5" spans="1:19">
+    <row r="5" spans="1:17">
       <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5">
+        <v>-1439.34</v>
+      </c>
+      <c r="C5">
+        <v>0.0431</v>
+      </c>
+      <c r="D5" t="s">
         <v>19</v>
       </c>
-      <c r="B5">
-        <v>-2496.6167</v>
-      </c>
-      <c r="C5">
-        <v>-1796.67</v>
-      </c>
-      <c r="D5">
-        <v>40000</v>
-      </c>
       <c r="E5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F5">
-        <v>1.6254</v>
+        <v>1.3389</v>
       </c>
       <c r="G5">
-        <v>0.0453</v>
+        <v>0.0255</v>
       </c>
       <c r="H5">
-        <v>0.3162</v>
+        <v>0.3145</v>
       </c>
       <c r="I5">
-        <v>0.0615</v>
+        <v>0.0353</v>
       </c>
       <c r="J5">
-        <v>0.1159</v>
+        <v>0.3211</v>
       </c>
       <c r="K5">
-        <v>0.0311</v>
+        <v>0.0205</v>
       </c>
       <c r="L5">
-        <v>0.9353</v>
+        <v>2.5898</v>
       </c>
       <c r="M5">
-        <v>0.0469</v>
+        <v>0.054</v>
       </c>
       <c r="N5">
-        <v>0.0271</v>
+        <v>0.0195</v>
       </c>
       <c r="O5">
-        <v>0.0443</v>
+        <v>0.0157</v>
       </c>
       <c r="P5">
+        <v>7.1852</v>
+      </c>
+      <c r="Q5">
+        <v>0.9219000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6">
+        <v>36.3173</v>
+      </c>
+      <c r="C6">
+        <v>0.0309</v>
+      </c>
+      <c r="D6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6">
+        <v>0.0113</v>
+      </c>
+      <c r="G6">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="H6">
+        <v>0.0045</v>
+      </c>
+      <c r="I6">
+        <v>0.0013</v>
+      </c>
+      <c r="J6">
+        <v>0.0047</v>
+      </c>
+      <c r="K6">
         <v>0.0009</v>
       </c>
-      <c r="Q5">
-        <v>0.1479</v>
-      </c>
-      <c r="R5">
-        <v>1.8812</v>
-      </c>
-      <c r="S5">
-        <v>0.1888</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19">
-      <c r="A6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6">
-        <v>858.2936</v>
-      </c>
-      <c r="C6">
-        <v>23.6276</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6">
-        <v>0.003</v>
-      </c>
-      <c r="G6">
-        <v>0.0005</v>
-      </c>
-      <c r="H6">
-        <v>0.0011</v>
-      </c>
-      <c r="I6">
-        <v>0.002</v>
-      </c>
-      <c r="J6">
-        <v>0.0018</v>
-      </c>
-      <c r="K6">
-        <v>0.0005999999999999999</v>
-      </c>
       <c r="L6">
-        <v>0.0049</v>
+        <v>0.0273</v>
       </c>
       <c r="M6">
-        <v>0.0001</v>
+        <v>0.004</v>
       </c>
       <c r="N6">
-        <v>0.0004</v>
+        <v>0.0008</v>
       </c>
       <c r="O6">
-        <v>0.0027</v>
+        <v>0.0017</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>0.0786</v>
       </c>
       <c r="Q6">
-        <v>0.0021</v>
-      </c>
-      <c r="R6">
-        <v>0.017</v>
-      </c>
-      <c r="S6">
-        <v>0.0014</v>
+        <v>0.0217</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tables/tabla_estabilidad_semillas_advi.xlsx
+++ b/outputs/tables/tabla_estabilidad_semillas_advi.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
   <si>
     <t>Semilla</t>
   </si>
@@ -55,12 +55,6 @@
     <t>sigma_phi_sd</t>
   </si>
   <si>
-    <t>sigma_theta_media</t>
-  </si>
-  <si>
-    <t>sigma_theta_sd</t>
-  </si>
-  <si>
     <t>alpha_disp_media</t>
   </si>
   <si>
@@ -82,7 +76,10 @@
     <t>Sí</t>
   </si>
   <si>
-    <t>Sí (3/3)</t>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Parcial</t>
   </si>
 </sst>
 </file>
@@ -440,10 +437,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -489,276 +486,240 @@
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:15">
       <c r="A2">
         <v>42</v>
       </c>
       <c r="B2">
-        <v>-1480.21</v>
+        <v>-1463.57</v>
       </c>
       <c r="C2">
-        <v>0.0076</v>
+        <v>0.0239</v>
       </c>
       <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
         <v>19</v>
       </c>
-      <c r="E2" t="s">
-        <v>21</v>
-      </c>
       <c r="F2">
-        <v>1.332005694650479</v>
+        <v>1.348215695543547</v>
       </c>
       <c r="G2">
-        <v>0.02516312780517108</v>
+        <v>0.02486440077844795</v>
       </c>
       <c r="H2">
-        <v>0.3125963688782021</v>
+        <v>0.3207415208061377</v>
       </c>
       <c r="I2">
-        <v>0.03574931768889927</v>
+        <v>0.03599026148128612</v>
       </c>
       <c r="J2">
-        <v>0.3214628363099949</v>
+        <v>0.3242401336987106</v>
       </c>
       <c r="K2">
-        <v>0.02141195909625017</v>
+        <v>0.01956712105023788</v>
       </c>
       <c r="L2">
-        <v>2.558342875251677</v>
+        <v>2.594779781848443</v>
       </c>
       <c r="M2">
-        <v>0.04939655817856773</v>
+        <v>0.05228587069472689</v>
       </c>
       <c r="N2">
-        <v>0.01922899493146631</v>
+        <v>6.981329354578524</v>
       </c>
       <c r="O2">
-        <v>0.01548166862814764</v>
-      </c>
-      <c r="P2">
-        <v>7.098867776710443</v>
-      </c>
-      <c r="Q2">
-        <v>0.8997399849432262</v>
+        <v>0.8838439947764355</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:15">
       <c r="A3">
         <v>123</v>
       </c>
       <c r="B3">
-        <v>-1410.77</v>
+        <v>-1403.44</v>
       </c>
       <c r="C3">
-        <v>0.0638</v>
+        <v>0.2038</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F3">
-        <v>1.351918969314986</v>
+        <v>1.345572138536676</v>
       </c>
       <c r="G3">
-        <v>0.02518978102619612</v>
+        <v>0.02644417649281535</v>
       </c>
       <c r="H3">
-        <v>0.319605347837042</v>
+        <v>0.3131006868787864</v>
       </c>
       <c r="I3">
-        <v>0.03630999987746104</v>
+        <v>0.03444523211483167</v>
       </c>
       <c r="J3">
-        <v>0.3161343921845154</v>
+        <v>0.3260877571401382</v>
       </c>
       <c r="K3">
-        <v>0.02059773163886027</v>
+        <v>0.01917872834715813</v>
       </c>
       <c r="L3">
-        <v>2.605343004977112</v>
+        <v>2.611742165145061</v>
       </c>
       <c r="M3">
-        <v>0.05651159955244913</v>
+        <v>0.05259287166703557</v>
       </c>
       <c r="N3">
-        <v>0.02047420476246393</v>
+        <v>7.553946328661643</v>
       </c>
       <c r="O3">
-        <v>0.0175495252095893</v>
-      </c>
-      <c r="P3">
-        <v>7.204266652214683</v>
-      </c>
-      <c r="Q3">
-        <v>0.9431206763929584</v>
+        <v>0.9755447672401087</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:15">
       <c r="A4">
         <v>999</v>
       </c>
       <c r="B4">
-        <v>-1427.04</v>
+        <v>-1566.81</v>
       </c>
       <c r="C4">
-        <v>0.0578</v>
+        <v>0.0541</v>
       </c>
       <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s">
         <v>19</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4">
+        <v>1.355457734654589</v>
+      </c>
+      <c r="G4">
+        <v>0.02816734406081621</v>
+      </c>
+      <c r="H4">
+        <v>0.328934224832281</v>
+      </c>
+      <c r="I4">
+        <v>0.03761217287548037</v>
+      </c>
+      <c r="J4">
+        <v>0.3314744399487521</v>
+      </c>
+      <c r="K4">
+        <v>0.0204700482263286</v>
+      </c>
+      <c r="L4">
+        <v>2.630751287642934</v>
+      </c>
+      <c r="M4">
+        <v>0.05140556772530547</v>
+      </c>
+      <c r="N4">
+        <v>7.223352763380353</v>
+      </c>
+      <c r="O4">
+        <v>0.9118138698189874</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5">
+        <v>-1477.94</v>
+      </c>
+      <c r="C5">
+        <v>0.0939</v>
+      </c>
+      <c r="D5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s">
         <v>21</v>
       </c>
-      <c r="F4">
-        <v>1.332831010468481</v>
-      </c>
-      <c r="G4">
-        <v>0.02625027291831595</v>
-      </c>
-      <c r="H4">
-        <v>0.3112868222927571</v>
-      </c>
-      <c r="I4">
-        <v>0.03383968101270034</v>
-      </c>
-      <c r="J4">
-        <v>0.3255962606921124</v>
-      </c>
-      <c r="K4">
-        <v>0.01962156322285576</v>
-      </c>
-      <c r="L4">
-        <v>2.605821791190158</v>
-      </c>
-      <c r="M4">
-        <v>0.05622828872385578</v>
-      </c>
-      <c r="N4">
-        <v>0.01894117873855222</v>
-      </c>
-      <c r="O4">
-        <v>0.01417912455200152</v>
-      </c>
-      <c r="P4">
-        <v>7.252540700545737</v>
-      </c>
-      <c r="Q4">
-        <v>0.9228097371502897</v>
+      <c r="F5">
+        <v>1.3497</v>
+      </c>
+      <c r="G5">
+        <v>0.0265</v>
+      </c>
+      <c r="H5">
+        <v>0.3209</v>
+      </c>
+      <c r="I5">
+        <v>0.036</v>
+      </c>
+      <c r="J5">
+        <v>0.3273</v>
+      </c>
+      <c r="K5">
+        <v>0.0197</v>
+      </c>
+      <c r="L5">
+        <v>2.6124</v>
+      </c>
+      <c r="M5">
+        <v>0.0521</v>
+      </c>
+      <c r="N5">
+        <v>7.2529</v>
+      </c>
+      <c r="O5">
+        <v>0.9237</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5">
-        <v>-1439.34</v>
-      </c>
-      <c r="C5">
-        <v>0.0431</v>
-      </c>
-      <c r="D5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5">
-        <v>1.3389</v>
-      </c>
-      <c r="G5">
-        <v>0.0255</v>
-      </c>
-      <c r="H5">
-        <v>0.3145</v>
-      </c>
-      <c r="I5">
-        <v>0.0353</v>
-      </c>
-      <c r="J5">
-        <v>0.3211</v>
-      </c>
-      <c r="K5">
-        <v>0.0205</v>
-      </c>
-      <c r="L5">
-        <v>2.5898</v>
-      </c>
-      <c r="M5">
-        <v>0.054</v>
-      </c>
-      <c r="N5">
-        <v>0.0195</v>
-      </c>
-      <c r="O5">
-        <v>0.0157</v>
-      </c>
-      <c r="P5">
-        <v>7.1852</v>
-      </c>
-      <c r="Q5">
-        <v>0.9219000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:15">
       <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6">
+        <v>82.6275</v>
+      </c>
+      <c r="C6">
+        <v>0.0963</v>
+      </c>
+      <c r="D6" t="s">
         <v>18</v>
       </c>
-      <c r="B6">
-        <v>36.3173</v>
-      </c>
-      <c r="C6">
-        <v>0.0309</v>
-      </c>
-      <c r="D6" t="s">
-        <v>20</v>
-      </c>
       <c r="E6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F6">
-        <v>0.0113</v>
+        <v>0.0051</v>
       </c>
       <c r="G6">
+        <v>0.0017</v>
+      </c>
+      <c r="H6">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="I6">
+        <v>0.0016</v>
+      </c>
+      <c r="J6">
+        <v>0.0038</v>
+      </c>
+      <c r="K6">
+        <v>0.0007</v>
+      </c>
+      <c r="L6">
+        <v>0.018</v>
+      </c>
+      <c r="M6">
         <v>0.0005999999999999999</v>
       </c>
-      <c r="H6">
-        <v>0.0045</v>
-      </c>
-      <c r="I6">
-        <v>0.0013</v>
-      </c>
-      <c r="J6">
-        <v>0.0047</v>
-      </c>
-      <c r="K6">
-        <v>0.0009</v>
-      </c>
-      <c r="L6">
-        <v>0.0273</v>
-      </c>
-      <c r="M6">
-        <v>0.004</v>
-      </c>
       <c r="N6">
-        <v>0.0008</v>
+        <v>0.2874</v>
       </c>
       <c r="O6">
-        <v>0.0017</v>
-      </c>
-      <c r="P6">
-        <v>0.0786</v>
-      </c>
-      <c r="Q6">
-        <v>0.0217</v>
+        <v>0.047</v>
       </c>
     </row>
   </sheetData>
